--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0925DEF-D199-0F46-9632-1713062B67D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239F2F38-0494-324D-A869-68BC36F05CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="194">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -249,9 +249,6 @@
   </si>
   <si>
     <t>2024-08-17</t>
-  </si>
-  <si>
-    <t>Private Party</t>
   </si>
   <si>
     <t>2024-08-24</t>
@@ -712,6 +709,12 @@
   </si>
   <si>
     <t>2028-09-09</t>
+  </si>
+  <si>
+    <t>Private Event</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1553,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1576,7 +1579,7 @@
     </row>
     <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>35</v>
@@ -1593,7 +1596,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="14"/>
       <c r="P8" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="17">
         <v>82.9</v>
@@ -1616,7 +1619,7 @@
     </row>
     <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>26</v>
@@ -1657,7 +1660,7 @@
     </row>
     <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>35</v>
@@ -1673,16 +1676,16 @@
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="P10" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="Q10" s="17">
         <v>65.7</v>
@@ -1705,7 +1708,7 @@
     </row>
     <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>31</v>
@@ -1726,7 +1729,7 @@
       </c>
       <c r="I11" s="14"/>
       <c r="P11" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="17">
         <v>57.8</v>
@@ -1746,7 +1749,7 @@
     </row>
     <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>35</v>
@@ -1763,7 +1766,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="14"/>
       <c r="P12" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="17">
         <v>69.099999999999994</v>
@@ -1786,24 +1789,24 @@
     </row>
     <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="14"/>
       <c r="P13" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="17">
         <v>75.7</v>
@@ -1823,7 +1826,7 @@
     </row>
     <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>26</v>
@@ -1861,24 +1864,24 @@
     </row>
     <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="Q15" s="17">
         <v>65.5</v>
@@ -1898,29 +1901,29 @@
     </row>
     <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="I16" s="14"/>
       <c r="M16" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" t="s">
         <v>74</v>
-      </c>
-      <c r="P16" t="s">
-        <v>75</v>
       </c>
       <c r="Q16" s="17">
         <v>74.099999999999994</v>
@@ -1940,13 +1943,13 @@
     </row>
     <row r="17" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="D17" s="10">
         <v>0.79166666666666663</v>
@@ -1956,12 +1959,12 @@
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="14"/>
       <c r="P17" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="17">
         <v>50.6</v>
@@ -1981,13 +1984,13 @@
     </row>
     <row r="18" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="D18" s="10">
         <v>0.875</v>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="14"/>
       <c r="P18" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q18" s="17">
         <v>5</v>
@@ -2022,13 +2025,13 @@
     </row>
     <row r="19" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="D19" s="10">
         <v>0.8125</v>
@@ -2038,14 +2041,14 @@
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I19" s="14"/>
       <c r="P19" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="17">
         <v>69.099999999999994</v>
@@ -2065,7 +2068,7 @@
     </row>
     <row r="20" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>31</v>
@@ -2086,7 +2089,7 @@
       </c>
       <c r="I20" s="14"/>
       <c r="P20" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="17">
         <v>52.4</v>
@@ -2106,7 +2109,7 @@
     </row>
     <row r="21" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>35</v>
@@ -2115,7 +2118,7 @@
         <v>36</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" s="10">
         <v>0.79166666666666663</v>
@@ -2126,16 +2129,16 @@
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>52</v>
-      </c>
       <c r="P21" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="17">
         <v>63.2</v>
@@ -2158,14 +2161,14 @@
     </row>
     <row r="22" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -2190,7 +2193,7 @@
     </row>
     <row r="23" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>40</v>
@@ -2199,27 +2202,27 @@
         <v>41</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" s="10">
         <v>0.75</v>
       </c>
       <c r="F23" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>98</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>99</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="14"/>
       <c r="L23" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M23" s="11" t="b">
         <v>1</v>
       </c>
       <c r="P23" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="17">
         <v>71.8</v>
@@ -2239,34 +2242,34 @@
     </row>
     <row r="24" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E24" s="10">
         <v>0.83333333333333337</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="14"/>
       <c r="L24" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M24" s="11" t="b">
         <v>1</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q24" s="17">
         <v>70.3</v>
@@ -2286,14 +2289,14 @@
     </row>
     <row r="25" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="10">
         <v>0.75</v>
@@ -2313,14 +2316,14 @@
     </row>
     <row r="26" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E26" s="10">
         <v>0.75</v>
@@ -2340,14 +2343,14 @@
     </row>
     <row r="27" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E27" s="10">
         <v>0.75</v>
@@ -2367,13 +2370,13 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D28" s="10">
         <v>0.79166666666666663</v>
@@ -2382,24 +2385,44 @@
         <v>0.875</v>
       </c>
       <c r="G28" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" t="s">
         <v>115</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="V28" t="s">
         <v>117</v>
       </c>
-      <c r="V28" t="s">
+      <c r="X28" t="s">
         <v>118</v>
       </c>
-      <c r="X28" t="s">
-        <v>119</v>
-      </c>
+    </row>
+    <row r="29" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="14"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="17"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="L30" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2422,13 +2445,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="28"/>
     </row>
@@ -2438,42 +2461,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2502,268 +2525,268 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" t="s">
         <v>165</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" t="s">
         <v>166</v>
-      </c>
-      <c r="C11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" t="s">
         <v>168</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" t="s">
         <v>169</v>
-      </c>
-      <c r="C12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" t="s">
         <v>171</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" t="s">
         <v>172</v>
-      </c>
-      <c r="C13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" t="s">
         <v>174</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
         <v>175</v>
-      </c>
-      <c r="C14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s">
         <v>177</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" t="s">
         <v>178</v>
-      </c>
-      <c r="C15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" t="s">
         <v>180</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
         <v>181</v>
-      </c>
-      <c r="C16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="C17" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="C18" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="C19" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAE2F2A-F05B-D34E-9245-48588CF72E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46749FCE-334A-8A4A-8CCE-3D3E3A8439B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="187">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -453,30 +453,6 @@
   </si>
   <si>
     <t>2028-09-09</t>
-  </si>
-  <si>
-    <t>2026-11-04</t>
-  </si>
-  <si>
-    <t>Wilmette Theatre</t>
-  </si>
-  <si>
-    <t>https://www.wilmettetheatre.com/</t>
-  </si>
-  <si>
-    <t>1122 Central Ave., Wilmette, IL 60091</t>
-  </si>
-  <si>
-    <t>Live Local Music</t>
-  </si>
-  <si>
-    <t>https://livelocal.music/</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>includes a free drink</t>
   </si>
   <si>
     <t>2026-10-03</t>
@@ -896,7 +872,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -951,9 +927,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="18" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1283,10 +1256,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="22" customWidth="1"/>
+    <col min="1" max="1" width="18" style="21" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="104.5" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -1310,20 +1283,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:24" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1386,13 +1359,13 @@
       <c r="U2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="W2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="23" t="s">
+      <c r="X2" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1948,7 +1921,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>76</v>
       </c>
@@ -1989,7 +1962,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>81</v>
       </c>
@@ -2030,7 +2003,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>86</v>
       </c>
@@ -2073,7 +2046,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>89</v>
       </c>
@@ -2114,7 +2087,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>91</v>
       </c>
@@ -2166,7 +2139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>94</v>
       </c>
@@ -2201,7 +2174,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>96</v>
       </c>
@@ -2250,7 +2223,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>102</v>
       </c>
@@ -2297,7 +2270,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>109</v>
       </c>
@@ -2306,7 +2279,7 @@
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2324,7 +2297,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>111</v>
       </c>
@@ -2351,7 +2324,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>112</v>
       </c>
@@ -2378,64 +2351,32 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+    <row r="28" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="14"/>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="17"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="L29" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="10">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E28" s="20">
-        <v>0.875</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="I28" t="s">
-        <v>117</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="V28" t="s">
-        <v>119</v>
-      </c>
-      <c r="X28" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="14"/>
-      <c r="O29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="17"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="L30" s="11" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2457,16 +2398,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="28"/>
+      <c r="A1" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="28"/>
+      <c r="A2" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="27"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
@@ -2474,42 +2415,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2538,268 +2479,268 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="C16" t="s">
-        <v>147</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B19" s="23" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24" t="s">
+      <c r="C19" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>185</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
